--- a/data/registered report/journals.xlsx
+++ b/data/registered report/journals.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ian-Hussey/git/measurement-trends-in-psychology/data/registered report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2E3D03-B023-0147-9713-D88850EB4F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1181D2-C620-0F42-B70B-10B66A89A871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41160" yWindow="1680" windowWidth="27640" windowHeight="19600" xr2:uid="{C4DAF39C-9970-0445-B8A0-71E471030EDF}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{C4DAF39C-9970-0445-B8A0-71E471030EDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
